--- a/planilhas/Checklist Auditoria E-commerce - V4.xlsx
+++ b/planilhas/Checklist Auditoria E-commerce - V4.xlsx
@@ -105,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -127,11 +127,55 @@
         <color rgb="00EAEAEC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00EAEAEC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00EAEAEC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EAEAEC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00EAEAEC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EAEAEC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00EAEAEC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EAEAEC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EAEAEC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -196,6 +240,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -798,9 +844,9 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:D12"/>
@@ -886,11 +932,11 @@
           <t>1.1  Infraestrutura, segurança e legal</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="11" t="n"/>
@@ -1066,11 +1112,11 @@
           <t>1.2  Performance (velocidade)</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="25" t="n"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="11" t="n"/>
@@ -1174,11 +1220,11 @@
           <t>1.3  Checkout e pagamento</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="25" t="n"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="13" t="n"/>
@@ -1354,11 +1400,11 @@
           <t>1.4  Frete e logística</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="25" t="n"/>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="13" t="n"/>
@@ -1510,11 +1556,11 @@
           <t>1.5  Catálogo / produtos (técnico)</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
+      <c r="B32" s="24" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="25" t="n"/>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="11" t="n"/>
@@ -1618,11 +1664,11 @@
           <t>1.6  Rastreamento / dados</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="25" t="n"/>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="13" t="n"/>
@@ -1846,11 +1892,11 @@
           <t>1.7  Integrações e automação</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="10" t="n"/>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="25" t="n"/>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="13" t="n"/>
@@ -1987,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2050,11 +2096,11 @@
           <t>2.1  Identidade visual e marca</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="11" t="n"/>
@@ -2134,11 +2180,11 @@
           <t>2.2  Home e navegação</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="25" t="n"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="11" t="n"/>
@@ -2266,11 +2312,11 @@
           <t>2.3  Página de produto (PDP)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="25" t="n"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="11" t="n"/>
@@ -2494,11 +2540,11 @@
           <t>2.4  Carrinho e checkout (UX)</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="25" t="n"/>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="11" t="n"/>
@@ -2674,11 +2720,11 @@
           <t>2.5  Confiança e credibilidade</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
+      <c r="B32" s="24" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="25" t="n"/>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="11" t="n"/>
@@ -2782,11 +2828,11 @@
           <t>2.6  Mobile UX</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="25" t="n"/>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="13" t="n"/>
@@ -2860,10 +2906,143 @@
       </c>
       <c r="F40" s="14" t="n"/>
     </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2.7  Copy e mensagem</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="24" t="n"/>
+      <c r="D41" s="24" t="n"/>
+      <c r="E41" s="24" t="n"/>
+      <c r="F41" s="25" t="n"/>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Nome do produto serve para a busca E para a pessoa</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Leia 10 nomes de produto do catálogo. Eles têm o termo que o cliente digita (tipo + característica principal) ou só o código interno/nome de fabricante? Nome que só o vendedor entende perde busca interna, busca do Google e Shopping. Corrija padronizando: o que é + característica que diferencia + variação, sem encher de palavra-chave repetida.</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="n"/>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Descrição vende o benefício antes da ficha técnica</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Leia a descrição de 5 produtos: ela começa dizendo o que aquilo resolve na vida de quem compra, ou já entra em medidas e composição? Ficha técnica é necessária, mas depois. Corrija reescrevendo o primeiro parágrafo com o problema que o produto resolve e para quem ele é; mova a especificação para um bloco próprio abaixo.</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n"/>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Copy de frete, prazo, troca e garantia reduz insegurança</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Abra as páginas e os blocos de frete, prazo, troca e garantia. Estão escritos para tranquilizar quem está comprando, ou copiados de texto jurídico? É onde a compra trava por medo. Corrija reescrevendo em linguagem direta (quanto tempo, quem paga o quê, o que fazer se der errado) e deixe o resumo visível na página de produto, não só no rodapé.</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="n"/>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Copy de checkout, carrinho abandonado e pós-compra</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Leia os textos do checkout (rótulos, mensagens de erro, aviso de segurança) e os e-mails/mensagens de carrinho abandonado e de confirmação. Costuma ser a copy mais esquecida da loja e uma das que mais recupera receita. Corrija: rótulo claro em cada campo, mensagem de erro que diz como resolver, e recuperação de carrinho com o produto, a objeção provável e um único CTA.</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n"/>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Teste da substituição na home e nas páginas institucionais</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Troque o nome da loja pelo de um concorrente e releia a home, a página Sobre e os banners. Se o texto continua funcionando, ele não comunica nada específico. Corrija trocando frase genérica por fato: há quanto tempo opera, o que vende de diferente, para quem, com que garantia.</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A37:F37"/>
@@ -2871,7 +3050,7 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E40">
+  <conditionalFormatting sqref="E4:E46">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -2888,7 +3067,7 @@
       <formula>"Pendente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D40">
+  <conditionalFormatting sqref="D4:D46">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>"Crítico"</formula>
     </cfRule>
@@ -2899,16 +3078,16 @@
       <formula>"Bom ter"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A40">
+  <conditionalFormatting sqref="A4:A46">
     <cfRule type="expression" priority="9" dxfId="6">
       <formula>A4="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E4:E40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>_Listas!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="A4:A40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A4:A46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>_Listas!$B$1:$B$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -2985,11 +3164,11 @@
           <t>3.1  Estratégia de canal</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="11" t="n"/>
@@ -3069,11 +3248,11 @@
           <t>3.2  Oferta e produto</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="25" t="n"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="11" t="n"/>
@@ -3225,11 +3404,11 @@
           <t>3.3  Criativos e conteúdo</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="25" t="n"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="13" t="n"/>
@@ -3381,11 +3560,11 @@
           <t>3.4  Funil e mídia</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="25" t="n"/>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="11" t="n"/>
@@ -3513,11 +3692,11 @@
           <t>3.5  SEO e orgânico</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="25" t="n"/>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="11" t="n"/>
@@ -3739,11 +3918,11 @@
           <t>4.1  Confirmação e acompanhamento do pedido</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="11" t="n"/>
@@ -3823,11 +4002,11 @@
           <t>4.2  Retenção, recompra e LTV</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="25" t="n"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="11" t="n"/>
@@ -4051,11 +4230,11 @@
           <t>4.3  Encantamento (experiência que gera recompra e indicação)</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="25" t="n"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="11" t="n"/>
@@ -4441,6 +4620,11 @@
           <t xml:space="preserve">1. </t>
         </is>
       </c>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="25" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
@@ -4448,6 +4632,11 @@
           <t xml:space="preserve">2. </t>
         </is>
       </c>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="25" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -4455,6 +4644,11 @@
           <t xml:space="preserve">3. </t>
         </is>
       </c>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="25" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
@@ -4469,6 +4663,11 @@
           <t xml:space="preserve">- </t>
         </is>
       </c>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="25" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
@@ -4476,6 +4675,11 @@
           <t xml:space="preserve">- </t>
         </is>
       </c>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="25" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
@@ -4483,12 +4687,17 @@
           <t xml:space="preserve">- </t>
         </is>
       </c>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A19:F19"/>
